--- a/mapping/npc_partyrelationshipgroup.xlsx
+++ b/mapping/npc_partyrelationshipgroup.xlsx
@@ -734,6 +734,41 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>PartyRelationshipGroup</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>PrimaryStreet</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Primary Street</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>nvarchar</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Household group primary address</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Sourced from the household Account's own Billing address (already carried in HouseholdAccount_Load) -- sample-reference-records showed real PartyRelationshipGroup records populate this 2-3/10 times.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -759,6 +794,41 @@
       <c r="G12" t="n">
         <v>100</v>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>PartyRelationshipGroup</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>PrimaryCity</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Primary City</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>nvarchar</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Household group primary address</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>See PrimaryStreet note.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -784,6 +854,41 @@
       <c r="G13" t="n">
         <v>100</v>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>PartyRelationshipGroup</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>PrimaryState</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Primary State</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>nvarchar</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Household group primary address</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>See PrimaryStreet note.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -809,6 +914,41 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>PartyRelationshipGroup</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>PrimaryPostalCode</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Primary Postal Code</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>nvarchar</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Household group primary address</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>See PrimaryStreet note.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -833,6 +973,41 @@
       </c>
       <c r="G15" t="n">
         <v>100</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>PartyRelationshipGroup</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>PrimaryCountry</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Primary Country</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>nvarchar</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Household group primary address</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>See PrimaryStreet note.</t>
+        </is>
       </c>
     </row>
     <row r="16">
